--- a/artfynd/A 38299-2022 artfynd.xlsx
+++ b/artfynd/A 38299-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38299-2022 artfynd.xlsx
+++ b/artfynd/A 38299-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7067863</v>
+        <v>7067872</v>
       </c>
       <c r="B2" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502765.6998256851</v>
+        <v>502859</v>
       </c>
       <c r="R2" t="n">
-        <v>6516829.094242219</v>
+        <v>6516158</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2013-07-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-07-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7067872</v>
+        <v>7067875</v>
       </c>
       <c r="B3" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502858.616143954</v>
+        <v>502859</v>
       </c>
       <c r="R3" t="n">
-        <v>6516158.445731083</v>
+        <v>6516158</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2013-07-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-07-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7067875</v>
+        <v>7067863</v>
       </c>
       <c r="B4" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2813</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502858.616143954</v>
+        <v>502766</v>
       </c>
       <c r="R4" t="n">
-        <v>6516158.445731083</v>
+        <v>6516829</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,19 +937,9 @@
           <t>2013-07-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-07-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 38299-2022 artfynd.xlsx
+++ b/artfynd/A 38299-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7067872</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7067875</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7067863</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>